--- a/data/industry_cache/20260905/industry_observation.xlsx
+++ b/data/industry_cache/20260905/industry_observation.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W32"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,35 +499,30 @@
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>模型意见</t>
+          <t>PE分位数得分</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>PE分位数得分</t>
+          <t>换手率分位数得分</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>换手率分位数得分</t>
+          <t>ROE同比得分</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>ROE同比得分</t>
+          <t>动量得分</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>动量得分</t>
+          <t>模型总得分</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
-        <is>
-          <t>模型总得分</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
         <is>
           <t>分析师意见</t>
         </is>
@@ -539,10 +534,8 @@
           <t>农林牧渔</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>801010</t>
-        </is>
+      <c r="B2" t="n">
+        <v>801010</v>
       </c>
       <c r="C2" t="n">
         <v>1.2382</v>
@@ -586,27 +579,22 @@
       <c r="P2" t="n">
         <v>-9.470000000000001</v>
       </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q2" t="n">
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S2" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
-      </c>
-      <c r="V2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W2" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -618,10 +606,8 @@
           <t>基础化工</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>801030</t>
-        </is>
+      <c r="B3" t="n">
+        <v>801030</v>
       </c>
       <c r="C3" t="n">
         <v>4.6221</v>
@@ -665,27 +651,22 @@
       <c r="P3" t="n">
         <v>11.27</v>
       </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q3" t="n">
+        <v>0</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T3" t="n">
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>1</v>
-      </c>
-      <c r="V3" t="n">
         <v>2</v>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -697,10 +678,8 @@
           <t>钢铁</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>801040</t>
-        </is>
+      <c r="B4" t="n">
+        <v>801040</v>
       </c>
       <c r="C4" t="n">
         <v>0.5908</v>
@@ -744,10 +723,8 @@
       <c r="P4" t="n">
         <v>-10.52</v>
       </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q4" t="n">
+        <v>0</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -756,15 +733,12 @@
         <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U4" t="n">
         <v>-1</v>
       </c>
-      <c r="V4" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="V4" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -776,10 +750,8 @@
           <t>有色金属</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>801050</t>
-        </is>
+      <c r="B5" t="n">
+        <v>801050</v>
       </c>
       <c r="C5" t="n">
         <v>5.5357</v>
@@ -823,27 +795,22 @@
       <c r="P5" t="n">
         <v>41.6</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q5" t="n">
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
-      <c r="W5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -855,10 +822,8 @@
           <t>电子</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>801080</t>
-        </is>
+      <c r="B6" t="n">
+        <v>801080</v>
       </c>
       <c r="C6" t="n">
         <v>19.5861</v>
@@ -902,27 +867,22 @@
       <c r="P6" t="n">
         <v>58.06</v>
       </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q6" t="n">
+        <v>0</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U6" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -934,10 +894,8 @@
           <t>汽车</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>801880</t>
-        </is>
+      <c r="B7" t="n">
+        <v>801880</v>
       </c>
       <c r="C7" t="n">
         <v>3.6038</v>
@@ -981,10 +939,8 @@
       <c r="P7" t="n">
         <v>-15.36</v>
       </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q7" t="n">
+        <v>0</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -993,15 +949,12 @@
         <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U7" t="n">
         <v>-1</v>
       </c>
-      <c r="V7" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1013,10 +966,8 @@
           <t>家用电器</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>801110</t>
-        </is>
+      <c r="B8" t="n">
+        <v>801110</v>
       </c>
       <c r="C8" t="n">
         <v>2.1156</v>
@@ -1060,10 +1011,8 @@
       <c r="P8" t="n">
         <v>-3.58</v>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q8" t="n">
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1072,15 +1021,12 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U8" t="n">
         <v>-1</v>
       </c>
-      <c r="V8" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1092,10 +1038,8 @@
           <t>食品饮料</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>801120</t>
-        </is>
+      <c r="B9" t="n">
+        <v>801120</v>
       </c>
       <c r="C9" t="n">
         <v>3.22</v>
@@ -1139,27 +1083,22 @@
       <c r="P9" t="n">
         <v>-18.96</v>
       </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q9" t="n">
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U9" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V9" t="n">
-        <v>0</v>
-      </c>
-      <c r="W9" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V9" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1171,10 +1110,8 @@
           <t>纺织服饰</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>801130</t>
-        </is>
+      <c r="B10" t="n">
+        <v>801130</v>
       </c>
       <c r="C10" t="n">
         <v>0.5145</v>
@@ -1218,10 +1155,8 @@
       <c r="P10" t="n">
         <v>-5.16</v>
       </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q10" t="n">
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -1230,15 +1165,12 @@
         <v>0</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
         <v>1</v>
       </c>
-      <c r="V10" t="n">
-        <v>1</v>
-      </c>
-      <c r="W10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1250,10 +1182,8 @@
           <t>轻工制造</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>801140</t>
-        </is>
+      <c r="B11" t="n">
+        <v>801140</v>
       </c>
       <c r="C11" t="n">
         <v>0.786</v>
@@ -1297,13 +1227,11 @@
       <c r="P11" t="n">
         <v>-6.81</v>
       </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q11" t="n">
+        <v>-1</v>
       </c>
       <c r="R11" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -1312,12 +1240,9 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
-      </c>
-      <c r="V11" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W11" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="V11" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1329,10 +1254,8 @@
           <t>医药生物</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>801150</t>
-        </is>
+      <c r="B12" t="n">
+        <v>801150</v>
       </c>
       <c r="C12" t="n">
         <v>6.298</v>
@@ -1376,27 +1299,22 @@
       <c r="P12" t="n">
         <v>-14.48</v>
       </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q12" t="n">
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S12" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U12" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V12" t="n">
         <v>-2</v>
       </c>
-      <c r="W12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1408,10 +1326,8 @@
           <t>公用事业</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>801160</t>
-        </is>
+      <c r="B13" t="n">
+        <v>801160</v>
       </c>
       <c r="C13" t="n">
         <v>2.4318</v>
@@ -1455,10 +1371,8 @@
       <c r="P13" t="n">
         <v>3.38</v>
       </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q13" t="n">
+        <v>0</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -1467,15 +1381,12 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U13" t="n">
         <v>-1</v>
       </c>
-      <c r="V13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W13" t="inlineStr">
+      <c r="V13" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1487,10 +1398,8 @@
           <t>交通运输</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>801170</t>
-        </is>
+      <c r="B14" t="n">
+        <v>801170</v>
       </c>
       <c r="C14" t="n">
         <v>1.8674</v>
@@ -1534,27 +1443,22 @@
       <c r="P14" t="n">
         <v>-8.08</v>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q14" t="n">
+        <v>0</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U14" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V14" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1566,10 +1470,8 @@
           <t>房地产</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>801180</t>
-        </is>
+      <c r="B15" t="n">
+        <v>801180</v>
       </c>
       <c r="C15" t="n">
         <v>0.8293</v>
@@ -1613,10 +1515,8 @@
       <c r="P15" t="n">
         <v>-15.9</v>
       </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q15" t="n">
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -1625,15 +1525,12 @@
         <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U15" t="n">
         <v>-1</v>
       </c>
-      <c r="V15" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W15" t="inlineStr">
+      <c r="V15" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1645,10 +1542,8 @@
           <t>商贸零售</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>801200</t>
-        </is>
+      <c r="B16" t="n">
+        <v>801200</v>
       </c>
       <c r="C16" t="n">
         <v>0.8341</v>
@@ -1692,27 +1587,22 @@
       <c r="P16" t="n">
         <v>-19.3</v>
       </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q16" t="n">
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
         <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>1</v>
-      </c>
-      <c r="V16" t="n">
         <v>2</v>
       </c>
-      <c r="W16" t="inlineStr">
+      <c r="V16" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1724,10 +1614,8 @@
           <t>社会服务</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>801210</t>
-        </is>
+      <c r="B17" t="n">
+        <v>801210</v>
       </c>
       <c r="C17" t="n">
         <v>0.5041</v>
@@ -1771,10 +1659,8 @@
       <c r="P17" t="n">
         <v>-15.49</v>
       </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q17" t="n">
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -1783,15 +1669,12 @@
         <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U17" t="n">
         <v>1</v>
       </c>
-      <c r="V17" t="n">
-        <v>1</v>
-      </c>
-      <c r="W17" t="inlineStr">
+      <c r="V17" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1803,10 +1686,8 @@
           <t>银行</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>801780</t>
-        </is>
+      <c r="B18" t="n">
+        <v>801780</v>
       </c>
       <c r="C18" t="n">
         <v>5.3188</v>
@@ -1850,10 +1731,8 @@
       <c r="P18" t="n">
         <v>-3.14</v>
       </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q18" t="n">
+        <v>0</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -1867,10 +1746,7 @@
       <c r="U18" t="n">
         <v>0</v>
       </c>
-      <c r="V18" t="n">
-        <v>0</v>
-      </c>
-      <c r="W18" t="inlineStr">
+      <c r="V18" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1882,10 +1758,8 @@
           <t>非银金融</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>801790</t>
-        </is>
+      <c r="B19" t="n">
+        <v>801790</v>
       </c>
       <c r="C19" t="n">
         <v>5.0816</v>
@@ -1929,27 +1803,22 @@
       <c r="P19" t="n">
         <v>-13.55</v>
       </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q19" t="n">
+        <v>1</v>
       </c>
       <c r="R19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U19" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V19" t="n">
-        <v>1</v>
-      </c>
-      <c r="W19" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V19" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -1961,10 +1830,8 @@
           <t>综合</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>801230</t>
-        </is>
+      <c r="B20" t="n">
+        <v>801230</v>
       </c>
       <c r="C20" t="n">
         <v>0.201</v>
@@ -2008,27 +1875,22 @@
       <c r="P20" t="n">
         <v>18.44</v>
       </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q20" t="n">
+        <v>-1</v>
       </c>
       <c r="R20" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T20" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U20" t="n">
         <v>-1</v>
       </c>
-      <c r="V20" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W20" t="inlineStr">
+      <c r="V20" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2040,10 +1902,8 @@
           <t>建筑材料</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>801710</t>
-        </is>
+      <c r="B21" t="n">
+        <v>801710</v>
       </c>
       <c r="C21" t="n">
         <v>0.8707</v>
@@ -2087,27 +1947,22 @@
       <c r="P21" t="n">
         <v>16.36</v>
       </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q21" t="n">
+        <v>-1</v>
       </c>
       <c r="R21" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U21" t="n">
-        <v>1</v>
-      </c>
-      <c r="V21" t="n">
-        <v>0</v>
-      </c>
-      <c r="W21" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V21" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2119,10 +1974,8 @@
           <t>建筑装饰</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>801720</t>
-        </is>
+      <c r="B22" t="n">
+        <v>801720</v>
       </c>
       <c r="C22" t="n">
         <v>1.2942</v>
@@ -2166,27 +2019,22 @@
       <c r="P22" t="n">
         <v>-5.46</v>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q22" t="n">
+        <v>-1</v>
       </c>
       <c r="R22" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U22" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V22" t="n">
         <v>-2</v>
       </c>
-      <c r="W22" t="inlineStr">
+      <c r="V22" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2198,10 +2046,8 @@
           <t>电力设备</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>801730</t>
-        </is>
+      <c r="B23" t="n">
+        <v>801730</v>
       </c>
       <c r="C23" t="n">
         <v>8.2722</v>
@@ -2245,27 +2091,22 @@
       <c r="P23" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q23" t="n">
+        <v>0</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T23" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U23" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
-      </c>
-      <c r="W23" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V23" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2277,10 +2118,8 @@
           <t>机械设备</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>801890</t>
-        </is>
+      <c r="B24" t="n">
+        <v>801890</v>
       </c>
       <c r="C24" t="n">
         <v>6.2326</v>
@@ -2324,13 +2163,11 @@
       <c r="P24" t="n">
         <v>14.24</v>
       </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q24" t="n">
+        <v>-1</v>
       </c>
       <c r="R24" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -2339,12 +2176,9 @@
         <v>0</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
-      </c>
-      <c r="V24" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W24" t="inlineStr">
+        <v>-1</v>
+      </c>
+      <c r="V24" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2356,10 +2190,8 @@
           <t>国防军工</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>801740</t>
-        </is>
+      <c r="B25" t="n">
+        <v>801740</v>
       </c>
       <c r="C25" t="n">
         <v>2.6397</v>
@@ -2403,10 +2235,8 @@
       <c r="P25" t="n">
         <v>-8.66</v>
       </c>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q25" t="n">
+        <v>0</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -2415,15 +2245,12 @@
         <v>0</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U25" t="n">
         <v>1</v>
       </c>
-      <c r="V25" t="n">
-        <v>1</v>
-      </c>
-      <c r="W25" t="inlineStr">
+      <c r="V25" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2435,10 +2262,8 @@
           <t>计算机</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>801750</t>
-        </is>
+      <c r="B26" t="n">
+        <v>801750</v>
       </c>
       <c r="C26" t="n">
         <v>4.8667</v>
@@ -2482,10 +2307,8 @@
       <c r="P26" t="n">
         <v>-17.38</v>
       </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q26" t="n">
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -2494,15 +2317,12 @@
         <v>0</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U26" t="n">
         <v>-1</v>
       </c>
-      <c r="V26" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W26" t="inlineStr">
+      <c r="V26" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2514,10 +2334,8 @@
           <t>传媒</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>801760</t>
-        </is>
+      <c r="B27" t="n">
+        <v>801760</v>
       </c>
       <c r="C27" t="n">
         <v>1.7163</v>
@@ -2561,27 +2379,22 @@
       <c r="P27" t="n">
         <v>-13.58</v>
       </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q27" t="n">
+        <v>0</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U27" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2593,10 +2406,8 @@
           <t>通信</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>801770</t>
-        </is>
+      <c r="B28" t="n">
+        <v>801770</v>
       </c>
       <c r="C28" t="n">
         <v>5.8025</v>
@@ -2640,27 +2451,22 @@
       <c r="P28" t="n">
         <v>68.81999999999999</v>
       </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q28" t="n">
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U28" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="V28" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2672,10 +2478,8 @@
           <t>煤炭</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>801950</t>
-        </is>
+      <c r="B29" t="n">
+        <v>801950</v>
       </c>
       <c r="C29" t="n">
         <v>0.9435</v>
@@ -2719,27 +2523,22 @@
       <c r="P29" t="n">
         <v>28.02</v>
       </c>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>平配</t>
-        </is>
+      <c r="Q29" t="n">
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="S29" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="T29" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U29" t="n">
         <v>0</v>
       </c>
-      <c r="V29" t="n">
-        <v>0</v>
-      </c>
-      <c r="W29" t="inlineStr">
+      <c r="V29" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2751,10 +2550,8 @@
           <t>石油石化</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>801960</t>
-        </is>
+      <c r="B30" t="n">
+        <v>801960</v>
       </c>
       <c r="C30" t="n">
         <v>1.1932</v>
@@ -2798,27 +2595,22 @@
       <c r="P30" t="n">
         <v>23.68</v>
       </c>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q30" t="n">
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
-      </c>
-      <c r="V30" t="n">
-        <v>1</v>
-      </c>
-      <c r="W30" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V30" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2830,10 +2622,8 @@
           <t>环保</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>801970</t>
-        </is>
+      <c r="B31" t="n">
+        <v>801970</v>
       </c>
       <c r="C31" t="n">
         <v>0.8057</v>
@@ -2877,10 +2667,8 @@
       <c r="P31" t="n">
         <v>-0.63</v>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>低配</t>
-        </is>
+      <c r="Q31" t="n">
+        <v>0</v>
       </c>
       <c r="R31" t="n">
         <v>0</v>
@@ -2889,15 +2677,12 @@
         <v>0</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="U31" t="n">
         <v>-1</v>
       </c>
-      <c r="V31" t="n">
-        <v>-1</v>
-      </c>
-      <c r="W31" t="inlineStr">
+      <c r="V31" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
@@ -2909,10 +2694,8 @@
           <t>美容护理</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>801980</t>
-        </is>
+      <c r="B32" t="n">
+        <v>801980</v>
       </c>
       <c r="C32" t="n">
         <v>0.1838</v>
@@ -2956,27 +2739,22 @@
       <c r="P32" t="n">
         <v>-28.24</v>
       </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>高配</t>
-        </is>
+      <c r="Q32" t="n">
+        <v>1</v>
       </c>
       <c r="R32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T32" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="U32" t="n">
-        <v>-1</v>
-      </c>
-      <c r="V32" t="n">
-        <v>1</v>
-      </c>
-      <c r="W32" t="inlineStr">
+        <v>1</v>
+      </c>
+      <c r="V32" t="inlineStr">
         <is>
           <t>平配</t>
         </is>
